--- a/artfynd/A 46038-2024 artfynd.xlsx
+++ b/artfynd/A 46038-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112923170</v>
+        <v>120753441</v>
       </c>
       <c r="B2" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdstjärnhön, Jmt</t>
+          <t>Fisklösnan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452941</v>
+        <v>453053</v>
       </c>
       <c r="R2" t="n">
-        <v>7045235</v>
+        <v>7045456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112923168</v>
+        <v>120753423</v>
       </c>
       <c r="B3" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdstjärnhön, Jmt</t>
+          <t>Fisklösnan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453096</v>
+        <v>453211</v>
       </c>
       <c r="R3" t="n">
-        <v>7045312</v>
+        <v>7045331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112923157</v>
+        <v>120753424</v>
       </c>
       <c r="B4" t="n">
-        <v>56756</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdstjärnhön, Jmt</t>
+          <t>Fisklösnan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453203</v>
+        <v>453067</v>
       </c>
       <c r="R4" t="n">
-        <v>7045334</v>
+        <v>7045423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112923143</v>
+        <v>120753425</v>
       </c>
       <c r="B5" t="n">
-        <v>90631</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gårdstjärnhön, Jmt</t>
+          <t>Fisklösnan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453239</v>
+        <v>452974</v>
       </c>
       <c r="R5" t="n">
-        <v>7045364</v>
+        <v>7045475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112923158</v>
+        <v>120753426</v>
       </c>
       <c r="B6" t="n">
-        <v>56756</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gårdstjärnhön, Jmt</t>
+          <t>Fisklösnan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453064</v>
+        <v>452937</v>
       </c>
       <c r="R6" t="n">
-        <v>7045330</v>
+        <v>7045531</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,17 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112923159</v>
+        <v>120753438</v>
       </c>
       <c r="B7" t="n">
-        <v>56756</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gårdstjärnhön, Jmt</t>
+          <t>Fisklösnan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453014</v>
+        <v>452768</v>
       </c>
       <c r="R7" t="n">
-        <v>7045314</v>
+        <v>7045620</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,17 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112923144</v>
+        <v>120753434</v>
       </c>
       <c r="B8" t="n">
-        <v>90631</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gårdstjärnhön, Jmt</t>
+          <t>Fisklösnan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453100</v>
+        <v>453049</v>
       </c>
       <c r="R8" t="n">
-        <v>7045315</v>
+        <v>7045456</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112923169</v>
+        <v>112923143</v>
       </c>
       <c r="B9" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453000</v>
+        <v>453240</v>
       </c>
       <c r="R9" t="n">
-        <v>7045299</v>
+        <v>7045364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,50 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120753432</v>
+        <v>112923144</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fisklösnan, Jmt</t>
+          <t>Gårdstjärnhön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452971</v>
+        <v>453100</v>
       </c>
       <c r="R10" t="n">
-        <v>7045308</v>
+        <v>7045315</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,17 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120753435</v>
+        <v>120753428</v>
       </c>
       <c r="B11" t="n">
-        <v>79677</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>453081</v>
+        <v>452937</v>
       </c>
       <c r="R11" t="n">
-        <v>7045449</v>
+        <v>7045553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120753441</v>
+        <v>120753430</v>
       </c>
       <c r="B12" t="n">
-        <v>88015</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>453053</v>
+        <v>452820</v>
       </c>
       <c r="R12" t="n">
-        <v>7045456</v>
+        <v>7045610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,50 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120753428</v>
+        <v>112923168</v>
       </c>
       <c r="B13" t="n">
-        <v>91365</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fisklösnan, Jmt</t>
+          <t>Gårdstjärnhön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452937</v>
+        <v>453096</v>
       </c>
       <c r="R13" t="n">
-        <v>7045553</v>
+        <v>7045312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,12 +1807,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,50 +1844,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120753423</v>
+        <v>112923169</v>
       </c>
       <c r="B14" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fisklösnan, Jmt</t>
+          <t>Gårdstjärnhön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453211</v>
+        <v>453001</v>
       </c>
       <c r="R14" t="n">
-        <v>7045331</v>
+        <v>7045299</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,50 +1941,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120753430</v>
+        <v>112923170</v>
       </c>
       <c r="B15" t="n">
-        <v>91365</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fisklösnan, Jmt</t>
+          <t>Gårdstjärnhön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452820</v>
+        <v>452942</v>
       </c>
       <c r="R15" t="n">
-        <v>7045610</v>
+        <v>7045235</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,37 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120753424</v>
+        <v>120753440</v>
       </c>
       <c r="B16" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453067</v>
+        <v>452846</v>
       </c>
       <c r="R16" t="n">
-        <v>7045423</v>
+        <v>7045612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,37 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120753434</v>
+        <v>120753435</v>
       </c>
       <c r="B17" t="n">
-        <v>91122</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>453049</v>
+        <v>453081</v>
       </c>
       <c r="R17" t="n">
-        <v>7045456</v>
+        <v>7045449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,15 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120753425</v>
+        <v>112923156</v>
       </c>
       <c r="B18" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,34 +2248,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fisklösnan, Jmt</t>
+          <t>Gårdstjärnhön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452974</v>
+        <v>453265</v>
       </c>
       <c r="R18" t="n">
-        <v>7045475</v>
+        <v>7045337</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,12 +2302,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,15 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120753426</v>
+        <v>112923157</v>
       </c>
       <c r="B19" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,34 +2350,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fisklösnan, Jmt</t>
+          <t>Gårdstjärnhön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452937</v>
+        <v>453203</v>
       </c>
       <c r="R19" t="n">
-        <v>7045531</v>
+        <v>7045335</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2504,12 +2404,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,15 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120753438</v>
+        <v>112923158</v>
       </c>
       <c r="B20" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2552,34 +2452,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fisklösnan, Jmt</t>
+          <t>Gårdstjärnhön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452768</v>
+        <v>453064</v>
       </c>
       <c r="R20" t="n">
-        <v>7045620</v>
+        <v>7045330</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2606,12 +2506,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,62 +2543,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120753436</v>
+        <v>112923159</v>
       </c>
       <c r="B21" t="n">
-        <v>57369</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fisklösnan, Jmt</t>
+          <t>Gårdstjärnhön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452943</v>
+        <v>453014</v>
       </c>
       <c r="R21" t="n">
-        <v>7045333</v>
+        <v>7045314</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,12 +2608,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2752,15 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120753440</v>
+        <v>120753432</v>
       </c>
       <c r="B22" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2768,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2792,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452846</v>
+        <v>452971</v>
       </c>
       <c r="R22" t="n">
-        <v>7045612</v>
+        <v>7045308</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2720,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2856,6 +2744,115 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120753436</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fisklösnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>452943</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7045333</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46038-2024 artfynd.xlsx
+++ b/artfynd/A 46038-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753423</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753424</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753425</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753426</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753438</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753434</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923143</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923144</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753428</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753430</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923168</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923169</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923170</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753440</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753435</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923156</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923157</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923158</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2642,6 +2742,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112923159</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753432</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2853,8 +2963,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120753436</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>